--- a/Data/PFOA-Descriptors-20082025.xlsx
+++ b/Data/PFOA-Descriptors-20082025.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sousa.Javannikkhah\Desktop\Collaborations\MOF-ML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hsm24sch\Documents\ML_Discovery_Metal-Organic_Adsobents\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8377F57-D0BF-47AF-9302-DD7556730FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40251064-6D3C-4DAA-BC67-7E3446043F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4BB31547-DEC7-4C48-81A3-F0434BAFACDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{4BB31547-DEC7-4C48-81A3-F0434BAFACDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
   <si>
     <t>#</t>
   </si>
@@ -269,13 +270,37 @@
   </si>
   <si>
     <t>P4322</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>Density</t>
+  </si>
+  <si>
+    <t>PLD</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>GSA</t>
+  </si>
+  <si>
+    <t>Void_Fraction</t>
+  </si>
+  <si>
+    <t>Pore_Volume</t>
+  </si>
+  <si>
+    <t>HKUST-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -953,28 +978,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABB696E-6F8C-490A-9846-176BAA6065B3}">
   <dimension ref="A3:N35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.54296875" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="63.42578125" customWidth="1"/>
+    <col min="5" max="5" width="28.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="29.81640625" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" customWidth="1"/>
+    <col min="9" max="9" width="63.453125" customWidth="1"/>
     <col min="10" max="10" width="21" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
-    <col min="12" max="12" width="50.28515625" customWidth="1"/>
-    <col min="13" max="13" width="23.85546875" customWidth="1"/>
-    <col min="14" max="14" width="34.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.28515625" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="20.453125" customWidth="1"/>
+    <col min="12" max="12" width="50.26953125" customWidth="1"/>
+    <col min="13" max="13" width="23.81640625" customWidth="1"/>
+    <col min="14" max="14" width="34.7265625" customWidth="1"/>
+    <col min="15" max="15" width="23.26953125" customWidth="1"/>
+    <col min="17" max="17" width="9.1796875" customWidth="1"/>
+    <col min="19" max="19" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1"/>
-    <row r="4" spans="1:14" ht="18">
+    <row r="3" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -1018,7 +1043,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="18">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A5" s="9">
         <v>1</v>
       </c>
@@ -1062,7 +1087,7 @@
         <v>0.47786099999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="18">
+    <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A6" s="9">
         <v>2</v>
       </c>
@@ -1106,7 +1131,7 @@
         <v>0.20608299999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="18">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A7" s="9">
         <v>3</v>
       </c>
@@ -1150,7 +1175,7 @@
         <v>0.171321</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18">
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="9">
         <v>4</v>
       </c>
@@ -1194,7 +1219,7 @@
         <v>1.02311</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="18">
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A9" s="9">
         <v>5</v>
       </c>
@@ -1238,7 +1263,7 @@
         <v>0.83910200000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18">
+    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A10" s="9">
         <v>6</v>
       </c>
@@ -1282,7 +1307,7 @@
         <v>0.48770200000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="36">
+    <row r="11" spans="1:14" ht="35" x14ac:dyDescent="0.4">
       <c r="A11" s="9">
         <v>7</v>
       </c>
@@ -1326,7 +1351,7 @@
         <v>1.3433600000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="54">
+    <row r="12" spans="1:14" ht="35" x14ac:dyDescent="0.4">
       <c r="A12" s="9">
         <v>8</v>
       </c>
@@ -1370,7 +1395,7 @@
         <v>0.41265000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="18">
+    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A13" s="9">
         <v>9</v>
       </c>
@@ -1414,7 +1439,7 @@
         <v>0.68158799999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="18">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A14" s="9">
         <v>10</v>
       </c>
@@ -1458,7 +1483,7 @@
         <v>1.6818500000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18">
+    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="9">
         <v>11</v>
       </c>
@@ -1502,7 +1527,7 @@
         <v>0.58702399999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="18">
+    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="9">
         <v>12</v>
       </c>
@@ -1546,7 +1571,7 @@
         <v>0.48621399999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="18">
+    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="9">
         <v>13</v>
       </c>
@@ -1590,7 +1615,7 @@
         <v>1.08691</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="18">
+    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A18" s="9">
         <v>14</v>
       </c>
@@ -1634,7 +1659,7 @@
         <v>1.8046899999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="18">
+    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A19" s="9">
         <v>15</v>
       </c>
@@ -1678,7 +1703,7 @@
         <v>0.19426199999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="18">
+    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A20" s="9">
         <v>16</v>
       </c>
@@ -1722,7 +1747,7 @@
         <v>0.97489300000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18">
+    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A21" s="9">
         <v>17</v>
       </c>
@@ -1766,7 +1791,7 @@
         <v>1.8046899999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="18">
+    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A22" s="9">
         <v>18</v>
       </c>
@@ -1810,7 +1835,7 @@
         <v>0.30784600000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="18">
+    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A23" s="9">
         <v>19</v>
       </c>
@@ -1854,7 +1879,7 @@
         <v>0.69393499999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18">
+    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A24" s="9">
         <v>20</v>
       </c>
@@ -1898,7 +1923,7 @@
         <v>0.23114000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="18">
+    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A25" s="9">
         <v>21</v>
       </c>
@@ -1942,7 +1967,7 @@
         <v>0.72438999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="18">
+    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A26" s="9">
         <v>22</v>
       </c>
@@ -1986,7 +2011,7 @@
         <v>9.9996000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="18.75" thickBot="1">
+    <row r="27" spans="1:14" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="12">
         <v>23</v>
       </c>
@@ -2030,7 +2055,7 @@
         <v>0.44489000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.75">
+    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.4">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
@@ -2039,34 +2064,668 @@
       <c r="F28" s="24"/>
       <c r="I28" s="17"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="I29" s="17"/>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="24"/>
       <c r="H30" s="2"/>
       <c r="I30" s="17"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="5:6" ht="18.75">
+    <row r="33" spans="5:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="E33" s="1"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="5:6">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="5:6">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CB0576-1753-4ED9-85D2-35CD17D1489B}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>1.23478</v>
+      </c>
+      <c r="D2">
+        <v>3.8217500000000002</v>
+      </c>
+      <c r="E2">
+        <v>8.7030700000000003</v>
+      </c>
+      <c r="F2">
+        <v>2920.55</v>
+      </c>
+      <c r="G2">
+        <v>0.590055</v>
+      </c>
+      <c r="H2">
+        <v>0.47786099999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>2.0227300000000001</v>
+      </c>
+      <c r="D3">
+        <v>1.27596</v>
+      </c>
+      <c r="E3">
+        <v>7.3330599999999997</v>
+      </c>
+      <c r="F3">
+        <v>2383.4299999999998</v>
+      </c>
+      <c r="G3">
+        <v>0.41685</v>
+      </c>
+      <c r="H3">
+        <v>0.20608299999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>1.6404000000000001</v>
+      </c>
+      <c r="D4">
+        <v>1.0821400000000001</v>
+      </c>
+      <c r="E4">
+        <v>2.7181899999999999</v>
+      </c>
+      <c r="F4">
+        <v>4812.3900000000003</v>
+      </c>
+      <c r="G4">
+        <v>0.28103499999999998</v>
+      </c>
+      <c r="H4">
+        <v>0.171321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>0.72258999999999995</v>
+      </c>
+      <c r="D5">
+        <v>6.7338699999999996</v>
+      </c>
+      <c r="E5">
+        <v>12.96894</v>
+      </c>
+      <c r="F5">
+        <v>3474.86</v>
+      </c>
+      <c r="G5">
+        <v>0.73928499999999997</v>
+      </c>
+      <c r="H5">
+        <v>1.02311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>0.86177000000000004</v>
+      </c>
+      <c r="D6">
+        <v>6.6421900000000003</v>
+      </c>
+      <c r="E6">
+        <v>12.83075</v>
+      </c>
+      <c r="F6">
+        <v>3058.54</v>
+      </c>
+      <c r="G6">
+        <v>0.72311000000000003</v>
+      </c>
+      <c r="H6">
+        <v>0.83910200000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>1.2841</v>
+      </c>
+      <c r="D7">
+        <v>10.09089</v>
+      </c>
+      <c r="E7">
+        <v>15.638350000000001</v>
+      </c>
+      <c r="F7">
+        <v>2178.08</v>
+      </c>
+      <c r="G7">
+        <v>0.62626000000000004</v>
+      </c>
+      <c r="H7">
+        <v>0.48770200000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>0.58974000000000004</v>
+      </c>
+      <c r="D8">
+        <v>18.480149999999998</v>
+      </c>
+      <c r="E8">
+        <v>19.439679999999999</v>
+      </c>
+      <c r="F8">
+        <v>3429.84</v>
+      </c>
+      <c r="G8">
+        <v>0.79222499999999996</v>
+      </c>
+      <c r="H8">
+        <v>1.3433600000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>1.2692099999999999</v>
+      </c>
+      <c r="D9">
+        <v>2.0553499999999998</v>
+      </c>
+      <c r="E9">
+        <v>7.4208999999999996</v>
+      </c>
+      <c r="F9">
+        <v>3526.25</v>
+      </c>
+      <c r="G9">
+        <v>0.52373999999999998</v>
+      </c>
+      <c r="H9">
+        <v>0.41265000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10">
+        <v>1.02671</v>
+      </c>
+      <c r="D10">
+        <v>6.6295500000000001</v>
+      </c>
+      <c r="E10">
+        <v>14.50667</v>
+      </c>
+      <c r="F10">
+        <v>2708.09</v>
+      </c>
+      <c r="G10">
+        <v>0.69979499999999994</v>
+      </c>
+      <c r="H10">
+        <v>0.68158799999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>0.48604000000000003</v>
+      </c>
+      <c r="D11">
+        <v>28.351690000000001</v>
+      </c>
+      <c r="E11">
+        <v>28.81297</v>
+      </c>
+      <c r="F11">
+        <v>3605.15</v>
+      </c>
+      <c r="G11">
+        <v>0.81744499999999998</v>
+      </c>
+      <c r="H11">
+        <v>1.6818500000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>1.00403</v>
+      </c>
+      <c r="D12">
+        <v>5.9524699999999999</v>
+      </c>
+      <c r="E12">
+        <v>6.5194200000000002</v>
+      </c>
+      <c r="F12">
+        <v>3990.86</v>
+      </c>
+      <c r="G12">
+        <v>0.58938999999999997</v>
+      </c>
+      <c r="H12">
+        <v>0.58702399999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>1.1510499999999999</v>
+      </c>
+      <c r="D13">
+        <v>3.6290399999999998</v>
+      </c>
+      <c r="E13">
+        <v>8.3301700000000007</v>
+      </c>
+      <c r="F13">
+        <v>3579.42</v>
+      </c>
+      <c r="G13">
+        <v>0.55965500000000001</v>
+      </c>
+      <c r="H13">
+        <v>0.48621399999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>0.67864000000000002</v>
+      </c>
+      <c r="D14">
+        <v>8.4971300000000003</v>
+      </c>
+      <c r="E14">
+        <v>27.80996</v>
+      </c>
+      <c r="F14">
+        <v>3593.18</v>
+      </c>
+      <c r="G14">
+        <v>0.73762000000000005</v>
+      </c>
+      <c r="H14">
+        <v>1.08691</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15">
+        <v>0.45745999999999998</v>
+      </c>
+      <c r="D15">
+        <v>13.84071</v>
+      </c>
+      <c r="E15">
+        <v>34.154089999999997</v>
+      </c>
+      <c r="F15">
+        <v>3804.83</v>
+      </c>
+      <c r="G15">
+        <v>0.82557499999999995</v>
+      </c>
+      <c r="H15">
+        <v>1.8046899999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16">
+        <v>1.86975</v>
+      </c>
+      <c r="D16">
+        <v>1.1613800000000001</v>
+      </c>
+      <c r="E16">
+        <v>2.33487</v>
+      </c>
+      <c r="F16">
+        <v>4245.26</v>
+      </c>
+      <c r="G16">
+        <v>0.36321999999999999</v>
+      </c>
+      <c r="H16">
+        <v>0.19426199999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17">
+        <v>0.75909000000000004</v>
+      </c>
+      <c r="D17">
+        <v>8.8461599999999994</v>
+      </c>
+      <c r="E17">
+        <v>27.76155</v>
+      </c>
+      <c r="F17">
+        <v>3270.98</v>
+      </c>
+      <c r="G17">
+        <v>0.740035</v>
+      </c>
+      <c r="H17">
+        <v>0.97489300000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18">
+        <v>0.45745999999999998</v>
+      </c>
+      <c r="D18">
+        <v>13.84071</v>
+      </c>
+      <c r="E18">
+        <v>34.154089999999997</v>
+      </c>
+      <c r="F18">
+        <v>3804.83</v>
+      </c>
+      <c r="G18">
+        <v>0.82557499999999995</v>
+      </c>
+      <c r="H18">
+        <v>1.8046899999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19">
+        <v>1.44353</v>
+      </c>
+      <c r="D19">
+        <v>3.1292900000000001</v>
+      </c>
+      <c r="E19">
+        <v>4.34999</v>
+      </c>
+      <c r="F19">
+        <v>3930.34</v>
+      </c>
+      <c r="G19">
+        <v>0.44438499999999997</v>
+      </c>
+      <c r="H19">
+        <v>0.30784600000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <v>0.91649999999999998</v>
+      </c>
+      <c r="D20">
+        <v>3.5794800000000002</v>
+      </c>
+      <c r="E20">
+        <v>11.983090000000001</v>
+      </c>
+      <c r="F20">
+        <v>4995.87</v>
+      </c>
+      <c r="G20">
+        <v>0.63599000000000006</v>
+      </c>
+      <c r="H20">
+        <v>0.69393499999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21">
+        <v>1.5014099999999999</v>
+      </c>
+      <c r="D21">
+        <v>1.07376</v>
+      </c>
+      <c r="E21">
+        <v>2.3644699999999998</v>
+      </c>
+      <c r="F21">
+        <v>5397.31</v>
+      </c>
+      <c r="G21">
+        <v>0.34703499999999998</v>
+      </c>
+      <c r="H21">
+        <v>0.23114000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22">
+        <v>0.94884999999999997</v>
+      </c>
+      <c r="D22">
+        <v>5.2106300000000001</v>
+      </c>
+      <c r="E22">
+        <v>11.118880000000001</v>
+      </c>
+      <c r="F22">
+        <v>3706.74</v>
+      </c>
+      <c r="G22">
+        <v>0.68733999999999995</v>
+      </c>
+      <c r="H22">
+        <v>0.72438999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23">
+        <v>1.8661300000000001</v>
+      </c>
+      <c r="D23">
+        <v>0.62124999999999997</v>
+      </c>
+      <c r="E23">
+        <v>1.4970600000000001</v>
+      </c>
+      <c r="F23">
+        <v>4111.54</v>
+      </c>
+      <c r="G23">
+        <v>0.18660499999999999</v>
+      </c>
+      <c r="H23">
+        <v>9.9996000000000002E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>1.28067</v>
+      </c>
+      <c r="D24">
+        <v>6.39825</v>
+      </c>
+      <c r="E24">
+        <v>6.6202699999999997</v>
+      </c>
+      <c r="F24">
+        <v>3272.51</v>
+      </c>
+      <c r="G24">
+        <v>0.56975500000000001</v>
+      </c>
+      <c r="H24">
+        <v>0.44489000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
